--- a/reports/pdf_change_20261016.xlsx
+++ b/reports/pdf_change_20261016.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,947억   ·   현금 205억(4.6%)      당일 2026-10-16  vs  전영업일 2026-10-15      매수 4종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,418억      당일 2026-10-16  vs  전영업일 2026-10-15      매수 4종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>139</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>487827213</v>
+        <v>488320323</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-170</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1524797261</v>
+        <v>-1526338570</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>63</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>714136154</v>
+        <v>714858023</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-45</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1211759412</v>
+        <v>-1212984294</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>950696539</v>
+        <v>951657530</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-35</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-864517081</v>
+        <v>-865390960</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1535489256</v>
+        <v>1537041372</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-829718598</v>
+        <v>-830557301</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>-34</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1674584188</v>
+        <v>-1676276906</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>-27</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-410038001</v>
+        <v>-410452479</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>-26</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1469753287</v>
+        <v>-1471238956</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-924659552</v>
+        <v>-925594224</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>-15</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-246509880</v>
+        <v>-246759060</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>-12</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-437183788</v>
+        <v>-437625706</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-829817598</v>
+        <v>-830656401</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-879911573</v>
+        <v>-880801013</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1068,23 +1068,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-386693813</v>
+        <v>-768619786</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.24%</t>
+          <t>1.34%→1.15%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1096,23 +1096,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-767843628</v>
+        <v>-387084694</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.15%</t>
+          <t>0.33%→0.24%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
         <v>-5</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-730124646</v>
+        <v>-730862677</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1152,23 +1152,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-861299582</v>
+        <v>-1076226261</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.72%</t>
+          <t>2.92%→2.62%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1180,30 +1180,30 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1075139479</v>
+        <v>-862170209</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.62%</t>
+          <t>0.91%→0.72%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,990억   ·   현금 66억(2.3%)      당일 2026-10-16  vs  전영업일 2026-10-15      매수 2종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,871억      당일 2026-10-16  vs  전영업일 2026-10-15      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1299,7 +1299,7 @@
         <v>56</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1411284266</v>
+        <v>1411284586</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>-20</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-2740100517</v>
+        <v>-2740101137</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>51</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>825766656</v>
+        <v>825766843</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>-19</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-843866159</v>
+        <v>-843866350</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>-14</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2864120540</v>
+        <v>-2864121189</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,556억   ·   현금 39억(1.7%)      당일 2026-10-16  vs  전영업일 2026-10-15      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,260억      당일 2026-10-16  vs  전영업일 2026-10-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1432,7 +1432,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,913억   ·   현금 41억(2.2%)      당일 2026-10-16  vs  전영업일 2026-10-15      매수 2종목  /  매도 6종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,855억      당일 2026-10-16  vs  전영업일 2026-10-15      매수 2종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1528,7 +1528,7 @@
         <v>80</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>5579543417</v>
+        <v>5579541669</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>-235</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1867603555</v>
+        <v>-1867602970</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>5731211401</v>
+        <v>5731209606</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>-234</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1841731908</v>
+        <v>-1841731331</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1614,14 +1614,14 @@
       <c r="E39" s="17" t="n"/>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>인벤티지랩</t>
+          <t>인벤티지랩 ※</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-200</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1849889807</v>
+        <v>-1849889227</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>-140</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-4681025511</v>
+        <v>-4681024044</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>-58</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1861533006</v>
+        <v>-1861532422</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>-23</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1880721304</v>
+        <v>-1880720714</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 296억   ·   현금 3억(1.1%)      당일 2026-10-16  vs  전영업일 2026-10-15      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 263억      당일 2026-10-16  vs  전영업일 2026-10-15      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -1817,11 +1817,11 @@
         <v>17</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>63897900</v>
+        <v>53191268</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.70%</t>
+          <t>2.32%→2.53%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -1838,11 +1838,11 @@
         <v>-88</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-67450240</v>
+        <v>-58901005</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>8.25%→8.02%</t>
+          <t>8.10%→7.87%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -1861,11 +1861,11 @@
         <v>8</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>79006400</v>
+        <v>66088761</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.33%→2.60%</t>
+          <t>2.19%→2.45%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -1882,11 +1882,11 @@
         <v>-31</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-54625100</v>
+        <v>-49224871</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.71%</t>
+          <t>2.93%→2.74%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -1905,11 +1905,11 @@
         <v>6</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>70028400</v>
+        <v>59294965</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.32%→1.56%</t>
+          <t>1.26%→1.48%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -1926,11 +1926,11 @@
         <v>-8</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-67643200</v>
+        <v>-64641561</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2.46%→2.23%</t>
+          <t>2.64%→2.39%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">

--- a/reports/pdf_change_20261016.xlsx
+++ b/reports/pdf_change_20261016.xlsx
@@ -1068,23 +1068,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-768619786</v>
+        <v>-387084694</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.15%</t>
+          <t>0.33%→0.24%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>51→44</t>
+          <t>25→18</t>
         </is>
       </c>
     </row>
@@ -1096,23 +1096,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-387084694</v>
+        <v>-768619786</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.24%</t>
+          <t>1.34%→1.15%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>25→18</t>
+          <t>51→44</t>
         </is>
       </c>
     </row>
@@ -1152,23 +1152,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1076226261</v>
+        <v>-862170209</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.62%</t>
+          <t>0.91%→0.72%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1180,23 +1180,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-862170209</v>
+        <v>-1076226261</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.72%</t>
+          <t>2.92%→2.62%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261016.xlsx
+++ b/reports/pdf_change_20261016.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-830557301</v>
+        <v>-1676276906</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.20%</t>
+          <t>2.12%→1.73%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>68→34</t>
+          <t>182→148</t>
         </is>
       </c>
     </row>
@@ -844,23 +844,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1676276906</v>
+        <v>-830557301</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.73%</t>
+          <t>0.40%→0.20%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>182→148</t>
+          <t>68→34</t>
         </is>
       </c>
     </row>
@@ -1012,23 +1012,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-830656401</v>
+        <v>-880801013</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.34%</t>
+          <t>0.45%→0.27%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>25→14</t>
         </is>
       </c>
     </row>
@@ -1040,23 +1040,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-880801013</v>
+        <v>-830656401</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.27%</t>
+          <t>0.51%→0.34%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>25→14</t>
+          <t>30→19</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261016.xlsx
+++ b/reports/pdf_change_20261016.xlsx
@@ -1152,23 +1152,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-862170209</v>
+        <v>-1076226261</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.72%</t>
+          <t>2.92%→2.62%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1180,23 +1180,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1076226261</v>
+        <v>-862170209</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.62%</t>
+          <t>0.91%→0.72%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261016.xlsx
+++ b/reports/pdf_change_20261016.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: RISE, TIGER</t>
+          <t>캡처 8/10  ·  전일분: TIGER 기술이전  ·  대기: RISE, MIDAS</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1676276906</v>
+        <v>-830557301</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.73%</t>
+          <t>0.40%→0.20%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>182→148</t>
+          <t>68→34</t>
         </is>
       </c>
     </row>
@@ -844,23 +844,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-830557301</v>
+        <v>-1676276906</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.20%</t>
+          <t>2.12%→1.73%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>68→34</t>
+          <t>182→148</t>
         </is>
       </c>
     </row>
@@ -1012,23 +1012,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-880801013</v>
+        <v>-830656401</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.27%</t>
+          <t>0.51%→0.34%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>25→14</t>
+          <t>30→19</t>
         </is>
       </c>
     </row>
@@ -1040,23 +1040,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-830656401</v>
+        <v>-880801013</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.34%</t>
+          <t>0.45%→0.27%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>25→14</t>
         </is>
       </c>
     </row>
@@ -1152,23 +1152,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1076226261</v>
+        <v>-862170209</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.62%</t>
+          <t>0.91%→0.72%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1180,23 +1180,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-862170209</v>
+        <v>-1076226261</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.72%</t>
+          <t>2.92%→2.62%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1957,41 +1957,649 @@
       <c r="K51" s="20" t="n"/>
     </row>
     <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="19" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
-      <c r="G53" s="20" t="n"/>
-      <c r="H53" s="20" t="n"/>
-      <c r="I53" s="20" t="n"/>
-      <c r="J53" s="20" t="n"/>
-      <c r="K53" s="20" t="n"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억      ※전일분  PDF 2026-10-15  vs  2026-10-14      매수 2종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>172702044</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>6.47%→6.66%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>97→101</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="n"/>
+      <c r="H56" s="17" t="n"/>
+      <c r="I56" s="17" t="n"/>
+      <c r="J56" s="17" t="n"/>
+      <c r="K56" s="17" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>133308329</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>5.76%→5.91%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>84→87</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="17" t="n"/>
+      <c r="I57" s="17" t="n"/>
+      <c r="J57" s="17" t="n"/>
+      <c r="K57" s="17" t="n"/>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 766억      당일 2026-10-16  vs  전영업일 2026-10-15      매수 1종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>태웅</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>17145602</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>0.99%→1.05%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>182→186</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-13096322</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>0.90%→0.87%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>411→403</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 300억      당일 2026-10-16  vs  전영업일 2026-10-15      매수 4종목  /  매도 6종목</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="8" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>HLB이노베이션  (신규)</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>290975798</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.00%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>0→40</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>LS머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-181729974</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>2.21%→1.53%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>103→73</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>158023241</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>0.45%→1.03%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>8→17</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>한양디지텍</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-239015834</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>4.85%→4.23%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>98→82</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>190346668</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>0.35%→1.03%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>4→11</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-213555452</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>2.91%→2.03%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>15→11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>144838400</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>2.82%→3.60%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>31→36</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-15449429</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>3.94%→4.12%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>313→309</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="n"/>
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="17" t="n"/>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="17" t="n"/>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>동국산업</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-6919335</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>1.83%→1.81%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>307→303</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="n"/>
+      <c r="B72" s="17" t="n"/>
+      <c r="C72" s="17" t="n"/>
+      <c r="D72" s="17" t="n"/>
+      <c r="E72" s="17" t="n"/>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-205241858</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>3.84%→3.01%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>21→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="19" customHeight="1">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="n"/>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="20" t="n"/>
+      <c r="F74" s="20" t="n"/>
+      <c r="G74" s="20" t="n"/>
+      <c r="H74" s="20" t="n"/>
+      <c r="I74" s="20" t="n"/>
+      <c r="J74" s="20" t="n"/>
+      <c r="K74" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A53:K53"/>
+  <mergeCells count="27">
     <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A59:K59"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G25:K25"/>
     <mergeCell ref="A51:K51"/>
     <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G65:K65"/>
     <mergeCell ref="G45:K45"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G54:K54"/>
+    <mergeCell ref="G25:K25"/>
     <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G60:K60"/>
     <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_change_20261016.xlsx
+++ b/reports/pdf_change_20261016.xlsx
@@ -1012,23 +1012,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-830656401</v>
+        <v>-880801013</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.34%</t>
+          <t>0.45%→0.27%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>30→19</t>
+          <t>25→14</t>
         </is>
       </c>
     </row>
@@ -1040,23 +1040,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-880801013</v>
+        <v>-830656401</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.27%</t>
+          <t>0.51%→0.34%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>25→14</t>
+          <t>30→19</t>
         </is>
       </c>
     </row>
@@ -1152,23 +1152,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-862170209</v>
+        <v>-1076226261</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.91%→0.72%</t>
+          <t>2.92%→2.62%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>45→41</t>
         </is>
       </c>
     </row>
@@ -1180,23 +1180,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1076226261</v>
+        <v>-862170209</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.62%</t>
+          <t>0.91%→0.72%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>45→41</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -2435,23 +2435,23 @@
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-213555452</v>
+        <v>-15449429</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2.91%→2.03%</t>
+          <t>3.94%→4.12%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>313→309</t>
         </is>
       </c>
     </row>
@@ -2479,23 +2479,23 @@
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-15449429</v>
+        <v>-205241858</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>3.94%→4.12%</t>
+          <t>3.84%→3.01%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>313→309</t>
+          <t>21→17</t>
         </is>
       </c>
     </row>
@@ -2535,23 +2535,23 @@
       <c r="E72" s="17" t="n"/>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-205241858</v>
+        <v>-213555452</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>3.84%→3.01%</t>
+          <t>2.91%→2.03%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>21→17</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
